--- a/backend/product-import-template.xlsx
+++ b/backend/product-import-template.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t xml:space="preserve">product_key</t>
   </si>
@@ -58,9 +58,6 @@
     <t xml:space="preserve">gender</t>
   </si>
   <si>
-    <t xml:space="preserve">activity</t>
-  </si>
-  <si>
     <t xml:space="preserve">shoe_type</t>
   </si>
   <si>
@@ -154,9 +151,6 @@
     <t xml:space="preserve">men</t>
   </si>
   <si>
-    <t xml:space="preserve">road-running,gym</t>
-  </si>
-  <si>
     <t xml:space="preserve">tempo-run</t>
   </si>
   <si>
@@ -200,9 +194,6 @@
   </si>
   <si>
     <t xml:space="preserve">WH-0003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">road-running</t>
   </si>
   <si>
     <t xml:space="preserve">road,lightweight</t>
@@ -407,28 +398,25 @@
       <c r="Y1" t="s" s="1">
         <v>24</v>
       </c>
-      <c r="Z1" t="s" s="1">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>29</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>30</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
       </c>
       <c r="G2">
         <v>12000</v>
@@ -440,7 +428,7 @@
         <v>0.3</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K2">
         <v>50</v>
@@ -452,30 +440,30 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
         <v>33</v>
-      </c>
-      <c r="P2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
         <v>35</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>36</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>37</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>38</v>
       </c>
-      <c r="E3" t="s">
-        <v>39</v>
-      </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3">
         <v>4500</v>
@@ -484,7 +472,7 @@
         <v>0.25</v>
       </c>
       <c r="J3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K3">
         <v>200</v>
@@ -496,30 +484,30 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="s">
         <v>33</v>
-      </c>
-      <c r="P3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
         <v>41</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>42</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>43</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>44</v>
       </c>
-      <c r="E4" t="s">
-        <v>45</v>
-      </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4">
         <v>35000</v>
@@ -528,7 +516,7 @@
         <v>0.25</v>
       </c>
       <c r="J4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -537,90 +525,87 @@
         <v>0</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P4" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" t="s">
         <v>47</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="V4" t="s">
         <v>48</v>
       </c>
-      <c r="S4" t="s">
+      <c r="W4" t="s">
         <v>49</v>
       </c>
-      <c r="W4" t="s">
-        <v>50</v>
-      </c>
-      <c r="X4" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z4">
+      <c r="Y4">
         <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="V5" t="s">
+        <v>50</v>
       </c>
       <c r="W5" t="s">
-        <v>52</v>
-      </c>
-      <c r="X5" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z5">
+        <v>51</v>
+      </c>
+      <c r="Y5">
         <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="V6" t="s">
+        <v>52</v>
       </c>
       <c r="W6" t="s">
-        <v>54</v>
-      </c>
-      <c r="X6" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z6">
+        <v>53</v>
+      </c>
+      <c r="Y6">
         <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="V7" t="s">
+        <v>54</v>
       </c>
       <c r="W7" t="s">
-        <v>56</v>
-      </c>
-      <c r="X7" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="X7">
+        <v>37000</v>
       </c>
       <c r="Y7">
-        <v>37000</v>
-      </c>
-      <c r="Z7">
         <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
         <v>58</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>59</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>60</v>
       </c>
-      <c r="D8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" t="s">
-        <v>62</v>
-      </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8">
         <v>180000</v>
@@ -632,7 +617,7 @@
         <v>0.9</v>
       </c>
       <c r="J8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -641,145 +626,142 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q8" t="s">
+        <v>62</v>
+      </c>
+      <c r="R8" t="s">
+        <v>63</v>
+      </c>
+      <c r="S8" t="s">
         <v>64</v>
       </c>
-      <c r="R8" t="s">
+      <c r="T8" t="s">
         <v>65</v>
       </c>
-      <c r="S8" t="s">
+      <c r="U8" t="s">
         <v>66</v>
       </c>
-      <c r="T8" t="s">
+      <c r="V8" t="s">
         <v>67</v>
       </c>
-      <c r="U8" t="s">
+      <c r="W8" t="s">
         <v>68</v>
       </c>
-      <c r="V8" t="s">
-        <v>69</v>
-      </c>
-      <c r="W8" t="s">
-        <v>70</v>
-      </c>
-      <c r="X8" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z8">
+      <c r="Y8">
         <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="U9" t="s">
+        <v>66</v>
       </c>
       <c r="V9" t="s">
         <v>69</v>
       </c>
       <c r="W9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X9" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z9">
+        <v>70</v>
+      </c>
+      <c r="Y9">
         <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="U10" t="s">
+        <v>66</v>
       </c>
       <c r="V10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="W10" t="s">
-        <v>74</v>
-      </c>
-      <c r="X10" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z10">
+        <v>72</v>
+      </c>
+      <c r="Y10">
         <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="U11" t="s">
+        <v>73</v>
       </c>
       <c r="V11" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="W11" t="s">
-        <v>70</v>
-      </c>
-      <c r="X11" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z11">
+        <v>74</v>
+      </c>
+      <c r="Y11">
         <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="U12" t="s">
+        <v>73</v>
       </c>
       <c r="V12" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="W12" t="s">
-        <v>72</v>
-      </c>
-      <c r="X12" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z12">
+        <v>75</v>
+      </c>
+      <c r="Y12">
         <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="U13" t="s">
+        <v>76</v>
       </c>
       <c r="V13" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="W13" t="s">
-        <v>74</v>
-      </c>
-      <c r="X13" t="s">
-        <v>80</v>
+        <v>77</v>
+      </c>
+      <c r="X13">
+        <v>195000</v>
       </c>
       <c r="Y13">
-        <v>195000</v>
-      </c>
-      <c r="Z13">
         <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
         <v>81</v>
       </c>
-      <c r="B14" t="s">
+      <c r="E14" t="s">
         <v>82</v>
       </c>
-      <c r="C14" t="s">
+      <c r="F14" t="s">
         <v>83</v>
-      </c>
-      <c r="D14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" t="s">
-        <v>85</v>
-      </c>
-      <c r="F14" t="s">
-        <v>86</v>
       </c>
       <c r="G14">
         <v>420000</v>
@@ -788,7 +770,7 @@
         <v>1.5</v>
       </c>
       <c r="J14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -797,49 +779,49 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P14" t="s">
-        <v>89</v>
-      </c>
-      <c r="V14" t="s">
-        <v>69</v>
-      </c>
-      <c r="X14" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z14">
+        <v>86</v>
+      </c>
+      <c r="U14" t="s">
+        <v>66</v>
+      </c>
+      <c r="W14" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y14">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>81</v>
-      </c>
-      <c r="V15" t="s">
-        <v>91</v>
-      </c>
-      <c r="X15" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z15">
+        <v>78</v>
+      </c>
+      <c r="U15" t="s">
+        <v>88</v>
+      </c>
+      <c r="W15" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y15">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>81</v>
-      </c>
-      <c r="V16" t="s">
-        <v>93</v>
-      </c>
-      <c r="X16" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z16">
+        <v>78</v>
+      </c>
+      <c r="U16" t="s">
+        <v>90</v>
+      </c>
+      <c r="W16" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y16">
         <v>0</v>
       </c>
     </row>
